--- a/SCH-STH/Impact assessments/Senegal/2025/november/sn_sppa_impact_2511_4_qualite.xlsx
+++ b/SCH-STH/Impact assessments/Senegal/2025/november/sn_sppa_impact_2511_4_qualite.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Senegal\2025\november\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0820C7-06EB-4F6D-8063-6C16AF1745E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4230751-0FB8-47B4-9817-A7C3663688A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="267">
   <si>
     <t>type</t>
   </si>
@@ -213,9 +213,6 @@
     <t>test_set</t>
   </si>
   <si>
-    <t>select_one test_set</t>
-  </si>
-  <si>
     <t>Filtration d urine + Kato katz</t>
   </si>
   <si>
@@ -270,9 +267,6 @@
     <t>Code unique de l’enfant: Veuillez sélectionner le code tel que généré par le formulaire 2.</t>
   </si>
   <si>
-    <t>Test effectué sur l'enfant</t>
-  </si>
-  <si>
     <t>Schistosoma haematobium - Volume d’urine collectée (en ml )</t>
   </si>
   <si>
@@ -405,9 +399,6 @@
     <t>${r_site_code}</t>
   </si>
   <si>
-    <t>r_test</t>
-  </si>
-  <si>
     <t>r_note1</t>
   </si>
   <si>
@@ -456,18 +447,12 @@
     <t>r_note2</t>
   </si>
   <si>
-    <t>${r_test} = 'Filtration d urine + Kato katz'</t>
-  </si>
-  <si>
     <t>r_k_positif</t>
   </si>
   <si>
     <t>r_sch_man_sa</t>
   </si>
   <si>
-    <t>${r_test} = 'Filtration d urine + Kato katz' and ${r_k_positif} = 'Oui'</t>
-  </si>
-  <si>
     <t>r_sch_man_sb</t>
   </si>
   <si>
@@ -828,13 +813,16 @@
     <t>Douves </t>
   </si>
   <si>
-    <t>sn_sppa_impact_2511_4_qualite</t>
-  </si>
-  <si>
-    <t>(2025 Nov) - 4. SCH/STH – Contrôle Qualité</t>
-  </si>
-  <si>
-    <t>r2_sppa_2511</t>
+    <t>sn_sppa_impact_2511_4_qualite_v2</t>
+  </si>
+  <si>
+    <t>(2025 Nov) - 4. SCH/STH – Contrôle Qualité V2</t>
+  </si>
+  <si>
+    <t>${r_k_positif} = 'Oui'</t>
+  </si>
+  <si>
+    <t>r2_sppa_2511_2</t>
   </si>
 </sst>
 </file>
@@ -1509,28 +1497,28 @@
         <v>43</v>
       </c>
       <c r="N1" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="O1" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="P1" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="Q1" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="R1" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="S1" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="S1" s="19" t="s">
-        <v>74</v>
-      </c>
       <c r="T1" s="19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="U1" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="5" customFormat="1" ht="31.5">
@@ -1541,7 +1529,7 @@
         <v>42</v>
       </c>
       <c r="C2" s="34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>29</v>
@@ -1574,10 +1562,10 @@
         <v>13</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C3" s="34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="10"/>
@@ -1593,7 +1581,7 @@
       <c r="M3" s="17"/>
       <c r="N3" s="17"/>
       <c r="O3" s="17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="P3" s="17"/>
       <c r="Q3" s="17"/>
@@ -1606,10 +1594,10 @@
         <v>13</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C4" s="34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D4" s="34"/>
       <c r="E4" s="30"/>
@@ -1625,10 +1613,10 @@
       <c r="M4" s="30"/>
       <c r="N4" s="30"/>
       <c r="O4" s="17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="P4" s="30" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="Q4" s="30"/>
       <c r="R4" s="30"/>
@@ -1640,10 +1628,10 @@
         <v>13</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C5" s="34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D5" s="34"/>
       <c r="E5" s="30"/>
@@ -1659,11 +1647,11 @@
       <c r="M5" s="30"/>
       <c r="N5" s="30"/>
       <c r="O5" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="P5" s="30"/>
       <c r="Q5" s="30" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="R5" s="30"/>
       <c r="S5" s="30"/>
@@ -1674,10 +1662,10 @@
         <v>13</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C6" s="34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D6" s="34"/>
       <c r="E6" s="30"/>
@@ -1693,13 +1681,13 @@
       <c r="M6" s="30"/>
       <c r="N6" s="30"/>
       <c r="O6" s="17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P6" s="30"/>
       <c r="Q6" s="30"/>
       <c r="R6" s="30"/>
       <c r="S6" s="30" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="T6" s="30"/>
     </row>
@@ -1708,10 +1696,10 @@
         <v>13</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D7" s="34"/>
       <c r="E7" s="30"/>
@@ -1727,14 +1715,14 @@
       <c r="M7" s="30"/>
       <c r="N7" s="30"/>
       <c r="O7" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P7" s="30"/>
       <c r="Q7" s="30"/>
       <c r="R7" s="30"/>
       <c r="S7" s="30"/>
       <c r="T7" s="30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:21" s="5" customFormat="1">
@@ -1751,7 +1739,7 @@
       <c r="G8" s="23"/>
       <c r="H8" s="10"/>
       <c r="I8" s="17" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
@@ -1772,7 +1760,7 @@
         <v>55</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C9" s="26" t="s">
         <v>60</v>
@@ -1839,7 +1827,7 @@
       <c r="G11" s="23"/>
       <c r="H11" s="10"/>
       <c r="I11" s="17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
@@ -1860,20 +1848,20 @@
         <v>13</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C12" s="34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D12" s="34" t="s">
         <v>49</v>
       </c>
       <c r="E12" s="30"/>
       <c r="F12" s="30" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H12" s="30"/>
       <c r="I12" s="30"/>
@@ -1885,7 +1873,7 @@
       <c r="M12" s="30"/>
       <c r="N12" s="30"/>
       <c r="O12" s="17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="P12" s="30"/>
       <c r="Q12" s="30"/>
@@ -1893,28 +1881,20 @@
       <c r="S12" s="30"/>
       <c r="T12" s="30"/>
       <c r="U12" s="30" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:21" s="36" customFormat="1">
-      <c r="A13" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>82</v>
-      </c>
+      <c r="A13" s="30"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="34"/>
       <c r="D13" s="34"/>
       <c r="E13" s="30"/>
       <c r="F13" s="30"/>
       <c r="G13" s="34"/>
       <c r="H13" s="30"/>
       <c r="I13" s="30"/>
-      <c r="J13" s="30" t="s">
-        <v>12</v>
-      </c>
+      <c r="J13" s="30"/>
       <c r="K13" s="10"/>
       <c r="L13" s="37"/>
       <c r="M13" s="30"/>
@@ -1931,10 +1911,10 @@
         <v>44</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D14" s="41"/>
       <c r="E14" s="39"/>
@@ -1956,16 +1936,16 @@
     </row>
     <row r="15" spans="1:21" s="36" customFormat="1" ht="31.5">
       <c r="A15" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="34" t="s">
         <v>130</v>
-      </c>
-      <c r="B15" s="38" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>133</v>
       </c>
       <c r="E15" s="30"/>
       <c r="F15" s="30"/>
@@ -2013,7 +1993,7 @@
         <v>44</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>46</v>
@@ -2038,13 +2018,13 @@
     </row>
     <row r="18" spans="1:20" s="36" customFormat="1" ht="31.5">
       <c r="A18" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="17"/>
@@ -2068,13 +2048,13 @@
     </row>
     <row r="19" spans="1:20" s="36" customFormat="1" ht="31.5">
       <c r="A19" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="17"/>
@@ -2101,17 +2081,17 @@
         <v>15</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="17"/>
       <c r="F20" s="10"/>
       <c r="G20" s="29"/>
       <c r="H20" s="17" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="10" t="s">
@@ -2155,10 +2135,10 @@
         <v>15</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>48</v>
@@ -2167,10 +2147,10 @@
       <c r="F22" s="10"/>
       <c r="G22" s="29"/>
       <c r="H22" s="17" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="J22" s="10" t="s">
         <v>12</v>
@@ -2215,7 +2195,7 @@
         <v>44</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C24" s="41" t="s">
         <v>45</v>
@@ -2224,9 +2204,7 @@
       <c r="E24" s="39"/>
       <c r="F24" s="39"/>
       <c r="G24" s="41"/>
-      <c r="H24" s="17" t="s">
-        <v>144</v>
-      </c>
+      <c r="H24" s="17"/>
       <c r="I24" s="39"/>
       <c r="J24" s="39"/>
       <c r="K24" s="39"/>
@@ -2242,21 +2220,19 @@
     </row>
     <row r="25" spans="1:20" s="36" customFormat="1">
       <c r="A25" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" s="41" t="s">
         <v>67</v>
-      </c>
-      <c r="B25" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>68</v>
       </c>
       <c r="D25" s="41"/>
       <c r="E25" s="39"/>
       <c r="F25" s="39"/>
       <c r="G25" s="41"/>
-      <c r="H25" s="17" t="s">
-        <v>144</v>
-      </c>
+      <c r="H25" s="17"/>
       <c r="I25" s="39"/>
       <c r="J25" s="39" t="s">
         <v>12</v>
@@ -2299,17 +2275,17 @@
         <v>15</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="17"/>
       <c r="F27" s="10"/>
       <c r="G27" s="29"/>
       <c r="H27" s="17" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="I27" s="17"/>
       <c r="J27" s="10" t="s">
@@ -2331,17 +2307,17 @@
         <v>15</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="17"/>
       <c r="F28" s="10"/>
       <c r="G28" s="29"/>
       <c r="H28" s="17" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="I28" s="17"/>
       <c r="J28" s="10" t="s">
@@ -2363,10 +2339,10 @@
         <v>15</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D29" s="34" t="s">
         <v>47</v>
@@ -2375,10 +2351,10 @@
       <c r="F29" s="30"/>
       <c r="G29" s="34"/>
       <c r="H29" s="30" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="I29" s="30" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="J29" s="10" t="s">
         <v>12</v>
@@ -2401,18 +2377,16 @@
         <v>53</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="17"/>
       <c r="F30" s="10"/>
       <c r="G30" s="29"/>
-      <c r="H30" s="30" t="s">
-        <v>144</v>
-      </c>
+      <c r="H30" s="30"/>
       <c r="I30" s="17" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J30" s="10"/>
       <c r="K30" s="17"/>
@@ -2431,18 +2405,16 @@
         <v>53</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="17"/>
       <c r="F31" s="10"/>
       <c r="G31" s="29"/>
-      <c r="H31" s="30" t="s">
-        <v>144</v>
-      </c>
+      <c r="H31" s="30"/>
       <c r="I31" s="17" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="J31" s="10"/>
       <c r="K31" s="17"/>
@@ -2483,17 +2455,17 @@
         <v>15</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="17"/>
       <c r="F33" s="10"/>
       <c r="G33" s="29"/>
       <c r="H33" s="17" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="I33" s="17"/>
       <c r="J33" s="10" t="s">
@@ -2515,17 +2487,17 @@
         <v>15</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="17"/>
       <c r="F34" s="10"/>
       <c r="G34" s="29"/>
       <c r="H34" s="17" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="I34" s="17"/>
       <c r="J34" s="10" t="s">
@@ -2547,10 +2519,10 @@
         <v>15</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>47</v>
@@ -2559,10 +2531,10 @@
       <c r="F35" s="10"/>
       <c r="G35" s="29"/>
       <c r="H35" s="17" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="I35" s="30" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="J35" s="10" t="s">
         <v>12</v>
@@ -2585,18 +2557,16 @@
         <v>53</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="17"/>
       <c r="F36" s="10"/>
       <c r="G36" s="29"/>
-      <c r="H36" s="30" t="s">
-        <v>144</v>
-      </c>
+      <c r="H36" s="30"/>
       <c r="I36" s="17" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="J36" s="10"/>
       <c r="K36" s="17"/>
@@ -2615,18 +2585,16 @@
         <v>53</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="17"/>
       <c r="F37" s="10"/>
       <c r="G37" s="29"/>
-      <c r="H37" s="30" t="s">
-        <v>144</v>
-      </c>
+      <c r="H37" s="30"/>
       <c r="I37" s="17" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J37" s="10"/>
       <c r="K37" s="17"/>
@@ -2667,17 +2635,17 @@
         <v>15</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="17"/>
       <c r="F39" s="10"/>
       <c r="G39" s="29"/>
       <c r="H39" s="17" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="I39" s="30"/>
       <c r="J39" s="10" t="s">
@@ -2699,17 +2667,17 @@
         <v>15</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="17"/>
       <c r="F40" s="10"/>
       <c r="G40" s="29"/>
       <c r="H40" s="17" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="I40" s="17"/>
       <c r="J40" s="10" t="s">
@@ -2731,10 +2699,10 @@
         <v>15</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>47</v>
@@ -2743,10 +2711,10 @@
       <c r="F41" s="10"/>
       <c r="G41" s="29"/>
       <c r="H41" s="17" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="I41" s="30" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="J41" s="10" t="s">
         <v>12</v>
@@ -2769,18 +2737,16 @@
         <v>53</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C42" s="8"/>
       <c r="D42" s="8"/>
       <c r="E42" s="17"/>
       <c r="F42" s="10"/>
       <c r="G42" s="29"/>
-      <c r="H42" s="30" t="s">
-        <v>144</v>
-      </c>
+      <c r="H42" s="30"/>
       <c r="I42" s="17" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="J42" s="10"/>
       <c r="K42" s="17"/>
@@ -2799,18 +2765,16 @@
         <v>53</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
       <c r="E43" s="17"/>
       <c r="F43" s="10"/>
       <c r="G43" s="29"/>
-      <c r="H43" s="30" t="s">
-        <v>144</v>
-      </c>
+      <c r="H43" s="30"/>
       <c r="I43" s="17" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="J43" s="10"/>
       <c r="K43" s="17"/>
@@ -2851,17 +2815,17 @@
         <v>15</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="17"/>
       <c r="F45" s="10"/>
       <c r="G45" s="29"/>
       <c r="H45" s="17" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="I45" s="17"/>
       <c r="J45" s="10" t="s">
@@ -2883,17 +2847,17 @@
         <v>15</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="17"/>
       <c r="F46" s="10"/>
       <c r="G46" s="29"/>
       <c r="H46" s="17" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="I46" s="17"/>
       <c r="J46" s="10" t="s">
@@ -2915,10 +2879,10 @@
         <v>15</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>47</v>
@@ -2927,10 +2891,10 @@
       <c r="F47" s="10"/>
       <c r="G47" s="29"/>
       <c r="H47" s="17" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="I47" s="30" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J47" s="10" t="s">
         <v>12</v>
@@ -2953,18 +2917,16 @@
         <v>53</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="17"/>
       <c r="F48" s="10"/>
       <c r="G48" s="29"/>
-      <c r="H48" s="30" t="s">
-        <v>144</v>
-      </c>
+      <c r="H48" s="30"/>
       <c r="I48" s="17" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="J48" s="10"/>
       <c r="K48" s="17"/>
@@ -2983,18 +2945,16 @@
         <v>53</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
       <c r="E49" s="17"/>
       <c r="F49" s="10"/>
       <c r="G49" s="29"/>
-      <c r="H49" s="30" t="s">
-        <v>144</v>
-      </c>
+      <c r="H49" s="30"/>
       <c r="I49" s="17" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="J49" s="10"/>
       <c r="K49" s="17"/>
@@ -3032,20 +2992,20 @@
     </row>
     <row r="51" spans="1:20" s="5" customFormat="1">
       <c r="A51" s="39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="17"/>
       <c r="F51" s="10"/>
       <c r="G51" s="29"/>
       <c r="H51" s="30" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="I51" s="17"/>
       <c r="J51" s="10" t="s">
@@ -3064,20 +3024,20 @@
     </row>
     <row r="52" spans="1:20" s="5" customFormat="1" ht="31.5">
       <c r="A52" s="10" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D52" s="8"/>
       <c r="E52" s="17"/>
       <c r="F52" s="10"/>
       <c r="G52" s="29"/>
       <c r="H52" s="30" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I52" s="17"/>
       <c r="J52" s="10"/>
@@ -3119,17 +3079,17 @@
         <v>15</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="17"/>
       <c r="F54" s="10"/>
       <c r="G54" s="29"/>
       <c r="H54" s="17" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I54" s="17"/>
       <c r="J54" s="10" t="s">
@@ -3151,17 +3111,17 @@
         <v>15</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="17"/>
       <c r="F55" s="10"/>
       <c r="G55" s="29"/>
       <c r="H55" s="17" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="I55" s="17"/>
       <c r="J55" s="10" t="s">
@@ -3183,10 +3143,10 @@
         <v>15</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>47</v>
@@ -3195,10 +3155,10 @@
       <c r="F56" s="10"/>
       <c r="G56" s="29"/>
       <c r="H56" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="I56" s="30" t="s">
         <v>187</v>
-      </c>
-      <c r="I56" s="30" t="s">
-        <v>192</v>
       </c>
       <c r="J56" s="10" t="s">
         <v>12</v>
@@ -3243,17 +3203,17 @@
         <v>15</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D58" s="8"/>
       <c r="E58" s="17"/>
       <c r="F58" s="10"/>
       <c r="G58" s="29"/>
       <c r="H58" s="17" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I58" s="17"/>
       <c r="J58" s="10" t="s">
@@ -3275,17 +3235,17 @@
         <v>15</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D59" s="8"/>
       <c r="E59" s="17"/>
       <c r="F59" s="10"/>
       <c r="G59" s="29"/>
       <c r="H59" s="17" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I59" s="17"/>
       <c r="J59" s="10" t="s">
@@ -3307,10 +3267,10 @@
         <v>15</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>47</v>
@@ -3319,10 +3279,10 @@
       <c r="F60" s="10"/>
       <c r="G60" s="29"/>
       <c r="H60" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="I60" s="30" t="s">
         <v>195</v>
-      </c>
-      <c r="I60" s="30" t="s">
-        <v>200</v>
       </c>
       <c r="J60" s="10" t="s">
         <v>12</v>
@@ -3367,17 +3327,17 @@
         <v>15</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="17"/>
       <c r="F62" s="10"/>
       <c r="G62" s="29"/>
       <c r="H62" s="17" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="I62" s="17"/>
       <c r="J62" s="10" t="s">
@@ -3399,17 +3359,17 @@
         <v>15</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="17"/>
       <c r="F63" s="10"/>
       <c r="G63" s="29"/>
       <c r="H63" s="17" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="I63" s="17"/>
       <c r="J63" s="10" t="s">
@@ -3431,10 +3391,10 @@
         <v>15</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>47</v>
@@ -3443,10 +3403,10 @@
       <c r="F64" s="10"/>
       <c r="G64" s="29"/>
       <c r="H64" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="I64" s="30" t="s">
         <v>203</v>
-      </c>
-      <c r="I64" s="30" t="s">
-        <v>208</v>
       </c>
       <c r="J64" s="10" t="s">
         <v>12</v>
@@ -3491,17 +3451,17 @@
         <v>15</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="17"/>
       <c r="F66" s="10"/>
       <c r="G66" s="29"/>
       <c r="H66" s="17" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="I66" s="17"/>
       <c r="J66" s="10" t="s">
@@ -3523,17 +3483,17 @@
         <v>15</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="17"/>
       <c r="F67" s="10"/>
       <c r="G67" s="29"/>
       <c r="H67" s="17" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="I67" s="17"/>
       <c r="J67" s="10" t="s">
@@ -3555,10 +3515,10 @@
         <v>15</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>47</v>
@@ -3567,10 +3527,10 @@
       <c r="F68" s="10"/>
       <c r="G68" s="29"/>
       <c r="H68" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="I68" s="30" t="s">
         <v>211</v>
-      </c>
-      <c r="I68" s="30" t="s">
-        <v>216</v>
       </c>
       <c r="J68" s="10" t="s">
         <v>12</v>
@@ -3615,17 +3575,17 @@
         <v>15</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D70" s="8"/>
       <c r="E70" s="17"/>
       <c r="F70" s="10"/>
       <c r="G70" s="29"/>
       <c r="H70" s="17" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="I70" s="17"/>
       <c r="J70" s="10" t="s">
@@ -3647,17 +3607,17 @@
         <v>15</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D71" s="8"/>
       <c r="E71" s="17"/>
       <c r="F71" s="10"/>
       <c r="G71" s="29"/>
       <c r="H71" s="17" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="I71" s="17"/>
       <c r="J71" s="10" t="s">
@@ -3679,10 +3639,10 @@
         <v>15</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>47</v>
@@ -3691,10 +3651,10 @@
       <c r="F72" s="10"/>
       <c r="G72" s="29"/>
       <c r="H72" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="I72" s="30" t="s">
         <v>219</v>
-      </c>
-      <c r="I72" s="30" t="s">
-        <v>224</v>
       </c>
       <c r="J72" s="10" t="s">
         <v>12</v>
@@ -3739,17 +3699,17 @@
         <v>15</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D74" s="8"/>
       <c r="E74" s="17"/>
       <c r="F74" s="10"/>
       <c r="G74" s="29"/>
       <c r="H74" s="17" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I74" s="17"/>
       <c r="J74" s="10" t="s">
@@ -3771,17 +3731,17 @@
         <v>15</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D75" s="8"/>
       <c r="E75" s="17"/>
       <c r="F75" s="10"/>
       <c r="G75" s="29"/>
       <c r="H75" s="17" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I75" s="17"/>
       <c r="J75" s="10" t="s">
@@ -3803,10 +3763,10 @@
         <v>15</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>47</v>
@@ -3815,10 +3775,10 @@
       <c r="F76" s="10"/>
       <c r="G76" s="29"/>
       <c r="H76" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="I76" s="30" t="s">
         <v>227</v>
-      </c>
-      <c r="I76" s="30" t="s">
-        <v>232</v>
       </c>
       <c r="J76" s="10" t="s">
         <v>12</v>
@@ -3863,17 +3823,17 @@
         <v>15</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D78" s="8"/>
       <c r="E78" s="17"/>
       <c r="F78" s="10"/>
       <c r="G78" s="29"/>
       <c r="H78" s="17" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I78" s="17"/>
       <c r="J78" s="10" t="s">
@@ -3895,17 +3855,17 @@
         <v>15</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D79" s="8"/>
       <c r="E79" s="17"/>
       <c r="F79" s="10"/>
       <c r="G79" s="29"/>
       <c r="H79" s="17" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="I79" s="17"/>
       <c r="J79" s="10" t="s">
@@ -3927,10 +3887,10 @@
         <v>15</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>47</v>
@@ -3939,10 +3899,10 @@
       <c r="F80" s="10"/>
       <c r="G80" s="29"/>
       <c r="H80" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="I80" s="30" t="s">
         <v>235</v>
-      </c>
-      <c r="I80" s="30" t="s">
-        <v>240</v>
       </c>
       <c r="J80" s="10" t="s">
         <v>12</v>
@@ -3987,17 +3947,17 @@
         <v>15</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D82" s="8"/>
       <c r="E82" s="17"/>
       <c r="F82" s="10"/>
       <c r="G82" s="29"/>
       <c r="H82" s="17" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="I82" s="17"/>
       <c r="J82" s="10" t="s">
@@ -4019,17 +3979,17 @@
         <v>15</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D83" s="8"/>
       <c r="E83" s="17"/>
       <c r="F83" s="10"/>
       <c r="G83" s="29"/>
       <c r="H83" s="17" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="I83" s="17"/>
       <c r="J83" s="10" t="s">
@@ -4051,10 +4011,10 @@
         <v>15</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>47</v>
@@ -4063,10 +4023,10 @@
       <c r="F84" s="10"/>
       <c r="G84" s="29"/>
       <c r="H84" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="I84" s="30" t="s">
         <v>243</v>
-      </c>
-      <c r="I84" s="30" t="s">
-        <v>248</v>
       </c>
       <c r="J84" s="10" t="s">
         <v>12</v>
@@ -4111,10 +4071,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="44" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C86" s="31" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D86" s="45"/>
       <c r="E86" s="46"/>
@@ -4163,7 +4123,7 @@
         <v>16</v>
       </c>
       <c r="B88" s="44" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C88" s="31"/>
       <c r="D88" s="45"/>
@@ -4189,7 +4149,7 @@
         <v>17</v>
       </c>
       <c r="B89" s="44" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C89" s="31"/>
       <c r="D89" s="45"/>
@@ -4365,10 +4325,10 @@
         <v>62</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -4376,7 +4336,7 @@
         <v>62</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>61</v>
@@ -4384,33 +4344,33 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>105</v>
-      </c>
-      <c r="B16" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>107</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="14"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="32" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D17" s="32"/>
       <c r="E17" s="14"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B19" s="9">
         <v>1</v>
@@ -4421,7 +4381,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B20" s="9">
         <v>2</v>
@@ -4432,7 +4392,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B21" s="9">
         <v>3</v>
@@ -4443,7 +4403,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B22" s="9">
         <v>4</v>
@@ -4454,7 +4414,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B23" s="9">
         <v>5</v>
@@ -4465,7 +4425,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B24" s="9">
         <v>6</v>
@@ -4476,7 +4436,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B25" s="9">
         <v>7</v>
@@ -4487,7 +4447,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B26" s="9">
         <v>8</v>
@@ -4498,7 +4458,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B27" s="9">
         <v>9</v>
@@ -4509,7 +4469,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B28" s="9">
         <v>10</v>
@@ -4520,90 +4480,90 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>253</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="6" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="6" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="6" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="6" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="6" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -4634,10 +4594,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="5" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C2" t="s">
         <v>27</v>
